--- a/artfynd/A 36480-2024 artfynd.xlsx
+++ b/artfynd/A 36480-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129166240</v>
       </c>
       <c r="B2" t="n">
-        <v>82897</v>
+        <v>82898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129166026</v>
       </c>
       <c r="B3" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129166190</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129165661</v>
       </c>
       <c r="B5" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129165588</v>
       </c>
       <c r="B6" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36480-2024 artfynd.xlsx
+++ b/artfynd/A 36480-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129166240</v>
       </c>
       <c r="B2" t="n">
-        <v>82898</v>
+        <v>82902</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129166026</v>
       </c>
       <c r="B3" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129166190</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129165661</v>
       </c>
       <c r="B5" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129165588</v>
       </c>
       <c r="B6" t="n">
-        <v>83011</v>
+        <v>83015</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36480-2024 artfynd.xlsx
+++ b/artfynd/A 36480-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129166240</v>
       </c>
       <c r="B2" t="n">
-        <v>82902</v>
+        <v>82871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129166026</v>
       </c>
       <c r="B3" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129165661</v>
       </c>
       <c r="B5" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129165588</v>
       </c>
       <c r="B6" t="n">
-        <v>83015</v>
+        <v>83005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36480-2024 artfynd.xlsx
+++ b/artfynd/A 36480-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129166240</v>
       </c>
       <c r="B2" t="n">
-        <v>82871</v>
+        <v>82873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129166026</v>
       </c>
       <c r="B3" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129166190</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129165661</v>
       </c>
       <c r="B5" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129165588</v>
       </c>
       <c r="B6" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
